--- a/www/download/COUNTRY.GBR.WIOD13.xlsx
+++ b/www/download/COUNTRY.GBR.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.633524869461459</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0.640311429707812</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.610612454449238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.603715279744235</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.617962958901194</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.65958277227438</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.694463734373446</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.66610712183995</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.611856564104196</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.545911129989382</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.549329817675818</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.542702541368262</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.499580378014237</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.539595512385694</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.639190041391055</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>27.913</t>
+          <t>0.0998192462865755</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.164</t>
+          <t>0.0687790253920271</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>0.16242977712851</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>0.0674644708279455</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.267</t>
+          <t>0.01126762902089</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.617</t>
+          <t>-0.0121075055104375</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.925</t>
+          <t>-0.0475169345585197</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30.106</t>
+          <t>-0.0693041499595339</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30.408</t>
+          <t>-0.135137579453755</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.703</t>
+          <t>-0.180394842557198</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>-0.172785354285181</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>31.398</t>
+          <t>-0.169678110303153</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>31.602</t>
+          <t>-0.13520175118397</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>31.674</t>
+          <t>-0.0333509963297783</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30.972</t>
+          <t>0.080960722136771</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23.964</t>
+          <t>0.66357581396995</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.245</t>
+          <t>0.67703651553952</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.808198976025105</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.156</t>
+          <t>0.676534459826351</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.577</t>
+          <t>0.567941851687406</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26.013</t>
+          <t>0.549718886498035</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.297</t>
+          <t>0.477719405382432</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.409</t>
+          <t>0.441679361846805</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.475</t>
+          <t>0.351598820970313</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.731</t>
+          <t>0.277393374197773</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27.093</t>
+          <t>0.288653801702946</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>0.284666668152845</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>27.438</t>
+          <t>0.32421853191313</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>27.505</t>
+          <t>0.519863390954081</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>26.766</t>
+          <t>0.629200248856359</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44993.802</t>
+          <t>0.946006519292477</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45389.552</t>
+          <t>0.939945925038883</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46176.543</t>
+          <t>1.13275618555328</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46487.59</t>
+          <t>1.01111674936171</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>46808.741</t>
+          <t>0.867501962497405</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>47050.896</t>
+          <t>0.830357701514389</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>47522.65</t>
+          <t>0.736725711140876</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47355.712</t>
+          <t>0.673076728656385</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>47271.276</t>
+          <t>0.571185089012112</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47631.936</t>
+          <t>0.485400786992551</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>48233.604</t>
+          <t>0.485074043347859</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>48510.801</t>
+          <t>0.485132168244663</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>48898.444</t>
+          <t>0.521240475642372</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>48638.184</t>
+          <t>0.716903101041263</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>47697.788</t>
+          <t>0.850162084090448</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>38627.754</t>
+          <t>51646833197.1015</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39074.066</t>
+          <t>52286385807.7155</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39982.918</t>
+          <t>50245496768.8572</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40493.614</t>
+          <t>50077757880.2695</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40906.739</t>
+          <t>50218836465.5059</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41325.285</t>
+          <t>48795460786.398</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>41761.52</t>
+          <t>47824992457.0374</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41540.623</t>
+          <t>46640237020.7945</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>41156.943</t>
+          <t>47191572707.9895</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>41469.329</t>
+          <t>48970110296.4596</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>42032.235</t>
+          <t>49954819980.8189</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42194.369</t>
+          <t>50441508077.643</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42455.417</t>
+          <t>50475243667.6069</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>42236.584</t>
+          <t>44824109822.6834</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>41220.09</t>
+          <t>40186870945.1193</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>24843568406.3242</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>25388683825.6383</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>24168487553.0262</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>26637338164.5381</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>28943881743.6636</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>30025761182.7746</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31835186732.9993</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>32734747774.8261</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>34764406212.126</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>37058272214.1654</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>37410638676.1209</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>37740729948.1165</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>36931554570.4039</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>32578600661.2488</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>29296454926.255</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>1037292.91374497</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>1013233.16426258</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>912096.556863017</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>879231.976478597</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>898758.020598977</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>901937.397670404</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>914117.702993001</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>837747.205511359</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>754358.128247717</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>667820.002178845</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>630953.743786967</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>593079.276231948</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>521725.789267342</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>477353.796875242</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>529508.885527107</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>164432.690496826</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>165514.765458267</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>165656.054853797</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>164715.105696112</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>166215.672267581</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>171255.184410343</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>166131.56181238</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>168122.325501128</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>179543.656737705</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>197777.106054743</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>213356.487523977</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>223515.060211958</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>252826.704202001</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>276193.934816072</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>252310.487244558</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>402084.699166096</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>410090.220355435</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>391552.404748227</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>388104.540171271</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>397649.049526667</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>402014.496986547</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>383694.195263882</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>382537.406438272</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>416923.170793829</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>476787.204239014</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>520905.413116193</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>551259.775700031</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>624056.905438893</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>613548.828702514</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>513101.940705768</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>0.554839193089609</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>0.539034726825145</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.65434093417811</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.520182455271668</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>0.413312132586082</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>0.376327641774193</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>0.311803822996247</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>0.269006973571893</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>0.183881647520094</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.119030284308386</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>0.123536959428809</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>0.118006171945475</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>0.149570274549424</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>0.296451767226101</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>0.406999241892006</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>212499.714423542</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>224850.50712233</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>236980.192946138</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>252738.581404539</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>235405.982950561</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>239573.487447957</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>220660.698319899</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>228590.088732335</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>249010.533575219</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>296735.317653387</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>300360.4609986</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>303542.538328749</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>357449.397718524</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.633524869461459</t>
+          <t>1036.70373920565</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.640311429707812</t>
+          <t>1047.17194578834</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.610612454449238</t>
+          <t>974.928904922398</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.603715279744235</t>
+          <t>1058.88607745819</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.617962958901194</t>
+          <t>1131.63708580614</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.65958277227438</t>
+          <t>1154.25983864893</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.694463734373446</t>
+          <t>1210.6014653002</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.66610712183995</t>
+          <t>1239.53000018275</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.611856564104196</t>
+          <t>1313.1031619311</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.545911129989382</t>
+          <t>1386.34066118609</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.549329817675818</t>
+          <t>1380.82304197102</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.542702541368262</t>
+          <t>1381.93811600573</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.499580378014237</t>
+          <t>1346.00023946366</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.539595512385694</t>
+          <t>1184.46103113066</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.639190041391055</t>
+          <t>1094.53989861223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>26960869737.1881</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>29152736597.5224</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>28169821662.2502</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>29816304027.7447</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>32481404898.9353</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>32871622254.4095</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>34065938299.8977</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>34748792544.8914</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>38378484302.5409</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>41376342705.2618</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>40171637085.3926</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>41557635463.8577</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>41095207318.9419</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>38570116724.85</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>32551982636.6995</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>25186349264.0863</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>26909953078.9205</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>25065993810.4803</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>26192339770.5231</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>27752913103.7498</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>27960575066.959</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>28644583739.6343</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>28332597785.0062</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>31052320854.7747</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>33310443024.8626</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>33144733137.4632</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>33406065741.0516</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>31306233113.3593</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.658</t>
+          <t>29329940304.8465</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>24557751415.4362</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>1774520473.10185</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>2242783518.60194</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.104</t>
+          <t>3103827851.76988</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3.286</t>
+          <t>3623964257.22156</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>4728491795.18553</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>4911047187.45046</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5421354560.26342</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>6416194759.88519</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>7326163447.76624</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.905</t>
+          <t>8065899680.39922</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>7026903947.92947</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.395</t>
+          <t>8151569722.80609</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.298</t>
+          <t>9788974205.58261</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9240176420.00355</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7994231221.26323</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>1611.90760533949</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>1611.63398952531</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1612.86479532656</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>1609.70003708337</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>1599.35642305417</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>1588.63972172234</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>1588.07163030566</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>1572.97221418347</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>1554.55873471084</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.942</t>
+          <t>1551.35718423535</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>1551.40572208536</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>1545.01534294111</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1547.32186482383</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>1535.5965970198</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>1540.01680756796</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1611.90760533949</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1611.63398952531</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1612.86479532656</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1609.70003708337</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1599.35642305417</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1588.63972172234</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1588.07163030566</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1572.97221418347</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1554.55873471084</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>1551.35718423535</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>1551.40572208536</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>1545.01534294111</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>1547.32186482383</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>1535.5965970198</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>1540.01680756796</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>302968.846362564</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>334168.171598558</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>362418.111046132</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>360604.193608908</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>365500.987238348</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>378672.434444504</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>368615.603568295</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>386747.802219923</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>443194.281960158</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>523620.734790844</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-17.28</t>
+          <t>547244.802844159</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-16.97</t>
+          <t>607572.724619445</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-13.53</t>
+          <t>703544.645994065</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>737461.648794785</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>572279.820996099</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>10061792312.6027</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>10785618927.8903</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>10278205510.1554</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>67.66</t>
+          <t>9659061187.01942</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>9621590379.10249</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>54.95</t>
+          <t>9922348584.43425</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>9526541711.66353</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>9045498948.06986</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>9413195613.4991</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>9385949516.97105</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>9148953563.04858</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>9448807539.27141</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>32.41</t>
+          <t>9481980075.0518</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>9250046467.10839</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>7711047731.9927</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>286045.401442143</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>313056.00743486</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>113.27</t>
+          <t>330836.790070265</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>345103.027382917</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>356517.811334066</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>83.01</t>
+          <t>372960.94236261</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>369101.953496387</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>391838.926787815</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>441883.051931132</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>534548.962064389</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>574998.747413278</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>632001.053436416</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>729681.255202372</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>748582.506174736</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>577281.317174778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>44993.802</t>
+          <t>34409711000.2605</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45389.552</t>
+          <t>36809205194.3437</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>46176.543</t>
+          <t>34126384013.6808</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>46487.59</t>
+          <t>37242306467.3972</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>46808.741</t>
+          <t>40752009861.5994</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>47050.896</t>
+          <t>41946111112.1787</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>47522.65</t>
+          <t>43668388373.6961</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>47355.712</t>
+          <t>44579984235.9491</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>47271.276</t>
+          <t>47600743034.6746</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>47631.936</t>
+          <t>52221651712.4312</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>48233.604</t>
+          <t>52755877629.5782</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>48510.801</t>
+          <t>53764516017.2861</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>48898.444</t>
+          <t>53178661766.2556</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>48638.184</t>
+          <t>48799940296.2194</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>47697.788</t>
+          <t>40747576923.9284</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>38627.754</t>
+          <t>16923.4449204217</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>39074.066</t>
+          <t>21112.1641636981</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39982.918</t>
+          <t>31581.3209758671</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>40493.614</t>
+          <t>15501.166225991</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>40906.739</t>
+          <t>8983.17590428165</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>41325.285</t>
+          <t>5711.49208189395</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>41761.52</t>
+          <t>-486.349928091777</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>41540.623</t>
+          <t>-5091.12456789178</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>41156.943</t>
+          <t>1311.23002902552</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>41469.329</t>
+          <t>-10928.2272735449</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>42032.235</t>
+          <t>-27753.9445691197</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>42194.369</t>
+          <t>-24428.3288169715</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>42455.417</t>
+          <t>-26136.6092083064</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>42236.584</t>
+          <t>-11120.8573799519</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>41220.09</t>
+          <t>-5001.49617867885</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>51648.76</t>
+          <t>-24347918687.6578</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>52292.527</t>
+          <t>-26023586266.4533</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50244.19</t>
+          <t>-23848178503.5254</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50074.114</t>
+          <t>-27583245280.3777</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>49525.017</t>
+          <t>-31130419482.4969</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>48808.677</t>
+          <t>-32023762527.7445</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>47832.68</t>
+          <t>-34141846662.0326</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>46649.529</t>
+          <t>-35534485287.8792</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>47197.401</t>
+          <t>-38187547421.1755</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>48973.449</t>
+          <t>-42835702195.4602</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>49956.998</t>
+          <t>-43606924066.5296</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>50443.253</t>
+          <t>-44315708478.0147</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>50477.65</t>
+          <t>-43696681691.2038</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>44826.639</t>
+          <t>-39549893829.111</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>40188.288</t>
+          <t>-33036529191.9357</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>497131.41044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>516670.71791</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>559244.04591</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>578765.90324</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>580780.17479</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>570505.03286</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>556625.6481</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>594832.15011</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>671468.75727</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>786803.00218</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>820056.55398</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>876941.47773</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>989863.96314</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>939376.0817</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>748813.66309</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21120.992</t>
+          <t>0.0470952753547024</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21103.085</t>
+          <t>0.0508804424029488</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21257.616</t>
+          <t>0.0554809263808922</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21253.457</t>
+          <t>0.0541179561267821</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20991.268</t>
+          <t>0.0578271294175202</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20786.503</t>
+          <t>0.0517769921084333</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20707.222</t>
+          <t>0.0547673795968436</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20498.035</t>
+          <t>0.0634693582337246</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20322.563</t>
+          <t>0.0680239315844092</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>20313.395</t>
+          <t>0.070349246983796</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20460.883</t>
+          <t>0.0675349092968399</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>20452.13</t>
+          <t>0.073821042652119</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>20449.24</t>
+          <t>0.07113262175852</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>20177.933</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>19761.315</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>609344.664262209</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>630766.500194064</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>704156.9451464</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>772019.549801978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>802302.130258525</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>806841.874751881</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>812416.796848852</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>881834.139782243</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1008231.40487965</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>1188319.79474407</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>1246278.60661961</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1327141.80120477</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1520317.19677425</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1439534.76037267</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1222888.6709742</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>24844.822</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>25390.317</t>
+          <t>729241.42651865</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24168.938</t>
+          <t>808232.241464891</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26636.347</t>
+          <t>880232.972086167</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28499.62</t>
+          <t>912758.829648804</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>30030.276</t>
+          <t>914475.288209213</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>31838.308</t>
+          <t>920938.425083602</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>32739.649</t>
+          <t>1002647.46318871</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>34767.348</t>
+          <t>1155969.91713234</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>37058.359</t>
+          <t>1362823.71365045</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>37411.613</t>
+          <t>1426225.38972571</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>37742.011</t>
+          <t>1522740.61097274</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>36934.586</t>
+          <t>1751292.93512564</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>32580.085</t>
+          <t>1657762.14653244</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>29297.368</t>
+          <t>1415851.85917085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>55.48</t>
+          <t>2763663.07938533</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>2874492.27388289</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>3103675.08207785</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>3285574.5211948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>3373543.96830096</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>3316084.58972</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>3249801.39741351</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>3578671.50054565</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>4115301.26386587</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>4904674.42694353</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>5124591.48593073</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>5394953.78242375</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>6297565.08436557</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>717204.956011211</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>739668.828371792</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>774560.756860511</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>809994.425963053</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>863088.268945091</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>893154.834139379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>890083.004289131</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>912867.143363989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>938179.502041366</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>978614.593700576</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>1009930.5478757</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>1041060.7112423</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>1032442.29769058</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1023323.8990226</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>609344.664262209</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>620383.656677345</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>643756.219903232</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>678743.230153769</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>711910.160967824</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>762181.992895343</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>789673.831616382</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>785132.006246717</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>799473.780840878</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>822591.64493767</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>858082.963645492</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>883884.88869262</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>909819.950108982</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>903492.72797568</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>889808.724787288</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>342655.188134818</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>371105.94570135</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>409174.961685109</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>430547.159193833</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>430488.346601196</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>411270.373080787</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>398643.805066398</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>455726.072201287</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>528949.505197663</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>641775.470289546</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>646449.28218429</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>701803.651607263</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>805411.712864362</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>793923.820217562</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>592527.649649153</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>38627753854.3556</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>39074066076.0412</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>39982918276.1454</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>40493614132.8693</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>40906739232.4566</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>41325285081.1633</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>41761519662.1478</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>41540623204.3714</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>41156942501.4695</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>41469328891.795</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>42032235228.4587</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>42194369015.7217</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>42455417327.0363</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>42236584401.0295</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>41220089871.3641</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>44993802000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>45389552000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>46176543000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>46487590000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>46808741000</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>47050896000</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>47522650000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>47355712000</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>47271276000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>47631936000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>48233604000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>48510801000</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>48898444000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>48638184000</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>47697788000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21120992059.2678</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21103085257.9798</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>21257616267.8664</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>21253457067.6056</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20991267736.0744</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20786503218.1709</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20707221502.5006</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20498034905.5748</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>20322563303.6011</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20313394762.9185</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20460883411.1362</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20452130215.4491</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>20449240107.8375</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>20177933177.2751</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>19761314827.713</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>27913387.7468886</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>28163684.9898958</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28630138.8273842</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28879660.1410479</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>29267235.4487518</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>29617096.5365194</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>29924752.1919734</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>30105879.5400161</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>30408163.3871446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>30703397.31174</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>31090257.8953786</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>31398264.8920847</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>31601986.058387</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>31673802.9339179</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>30972251.5790757</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23964000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24245000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24790000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>25156000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>25577000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>26013000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>26297000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>26409000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26475000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>26731000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>27093000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27310000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>27438000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>27505000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>26766000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>44993802000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>45389552000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>46176543000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>46487590000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>46808741000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>47050896000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>47522650000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>47355712000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>47271276000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>47631936000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>48233604000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>48510801000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>48898444000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>48638184000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>47697788000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>38627753854.3556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>39074066076.0412</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>39982918276.1454</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40493614132.8693</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>40906739232.4566</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>41325285081.1633</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>41761519662.1478</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>41540623204.3714</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>41156942501.4695</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>41469328891.795</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>42032235228.4587</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>42194369015.7217</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>42455417327.0363</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>42236584401.0295</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>41220089871.3641</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.277767528904053</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.28488409319564</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.299234247700508</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.316493571632793</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.329116537176529</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.347523843868929</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.350137638080635</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.360656736409175</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.361891037278401</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.355932378530736</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.361792155573614</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.372400404706165</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.389528465053993</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.399501116619149</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.398407637829891</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.415303017138807</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.416234283839518</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435409014035973</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.433675026228324</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.432040079440748</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.420134869664512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.412186031559375</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.413691429736799</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.431608389644541</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.446891177916702</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.444916896543453</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.442551596604485</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.422380180206385</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.417104646342857</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.427590105531019</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.30692945395714</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.298881622964842</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.265356738263519</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.249831402138882</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.238843383382723</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.232341286466559</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.23767633035999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.225651833854026</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.206500573077058</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.197176443552562</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.193290947882933</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.185047998689349</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.188091354739622</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.183394237037994</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.17400225663909</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.189766274996681</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.190379047097163</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.203799425594425</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.216388318268939</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.230560399126563</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.243414760669638</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.248715498768196</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.258058419418581</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.259437706930295</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.255510329270998</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.259812932362462</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.269235322839665</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.28630327573404</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.28719214049374</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.290226513831573</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.433241589076702</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.440991399183517</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.463079372051525</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.463273795379137</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.463675712205606</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.458116574755566</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.449818700886118</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.455396582149686</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.476733137253857</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.491909929449492</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.492288182470444</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.489822794062092</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.468380014306229</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.472070456315513</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.479810922968492</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.376992135926617</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.36862955371932</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.33312120235405</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.320337886351924</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.305763888667831</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.298468664574796</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.301465800345686</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.286544998431733</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.263829155815847</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.25257974127951</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.247898885167095</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.240941883098243</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.245316709959732</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.240737403190748</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.229962563199935</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2101260.81717</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2220947.3865</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2459925.23759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2637347.57813</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2712196.54421</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2687524.70806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2668744.08914</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2908661.31497</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3332392.14615</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3941733.15299</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4191589.31804</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4487219.69286</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5139696.58206</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4908990.5134</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4002420.38558</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1047516.88555</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1100347.37222</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1217407.20315</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1310780.13128</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1343247.17625</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1325745.66129</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1319582.23015</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1458373.53539</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1684919.42233</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2004599.18394</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2072674.67191</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2224544.26258</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2556704.64799</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2451685.96675</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2008379.50882</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1750849.27053902</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1797714.07422874</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1850266.51528009</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1921140.27809232</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1991368.44787993</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2066078.15091517</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2140835.62887224</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2215228.67333853</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2284620.07971019</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2361715.48426028</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2443562.40256436</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2531603.63459202</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2632783.32126529</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
